--- a/Q4/表2_Q4-3.xlsx
+++ b/Q4/表2_Q4-3.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="表2" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="表2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,7 +738,7 @@
         <v>2500</v>
       </c>
       <c r="F17" t="n">
-        <v>6483.9472</v>
+        <v>6500.2572</v>
       </c>
     </row>
     <row r="18">
@@ -748,7 +748,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4711.8449</v>
+        <v>4699.6269</v>
       </c>
       <c r="C18" t="n">
         <v>2139.7428</v>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6201.708</v>
+        <v>6234.0619</v>
       </c>
       <c r="F18" t="n">
         <v>216.288</v>
